--- a/结果/问题三_中继部署方案_新.xlsx
+++ b/结果/问题三_中继部署方案_新.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="38">
   <si>
     <t>中继ID</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>R05</t>
+  </si>
+  <si>
+    <t>R06</t>
   </si>
   <si>
     <t>服务区</t>
@@ -484,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -659,6 +662,35 @@
       </c>
       <c r="I6">
         <v>2.46578613275855</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>109.262083075</v>
+      </c>
+      <c r="C7">
+        <v>23.04700435</v>
+      </c>
+      <c r="D7">
+        <v>150</v>
+      </c>
+      <c r="E7">
+        <v>126.39</v>
+      </c>
+      <c r="F7">
+        <v>0.2275309462316984</v>
+      </c>
+      <c r="G7">
+        <v>2.211825</v>
+      </c>
+      <c r="H7">
+        <v>0.105325</v>
+      </c>
+      <c r="I7">
+        <v>2.544680946231699</v>
       </c>
     </row>
   </sheetData>
@@ -673,103 +705,103 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
@@ -777,26 +809,26 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -806,26 +838,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>10.76379651030906</v>
@@ -839,7 +871,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>10.76379651030906</v>
@@ -853,7 +885,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>10.76379651030906</v>
@@ -867,7 +899,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>10.76379651030906</v>
@@ -881,7 +913,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>8.289084246674548</v>
@@ -895,7 +927,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>8.289084246674548</v>
@@ -909,7 +941,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8">
         <v>8.289084246674548</v>
@@ -923,7 +955,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>8.289084246674548</v>
@@ -937,7 +969,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>14.21739692800409</v>
@@ -951,7 +983,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11">
         <v>14.21739692800409</v>
@@ -965,7 +997,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12">
         <v>14.21739692800409</v>
@@ -979,7 +1011,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>8.685717549233942</v>
@@ -993,7 +1025,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <v>8.685717549233942</v>
@@ -1007,7 +1039,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <v>8.685717549233942</v>
@@ -1021,7 +1053,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16">
         <v>12.0899687447572</v>
@@ -1031,6 +1063,62 @@
       </c>
       <c r="D16">
         <v>8.190190912408184</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>8.391647231234558</v>
+      </c>
+      <c r="C17">
+        <v>8.20225534987793</v>
+      </c>
+      <c r="D17">
+        <v>8.20225534987793</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18">
+        <v>8.391647231234558</v>
+      </c>
+      <c r="C18">
+        <v>14.12518081972306</v>
+      </c>
+      <c r="D18">
+        <v>8.391647231234558</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19">
+        <v>8.391647231234558</v>
+      </c>
+      <c r="C19">
+        <v>8.661945235942298</v>
+      </c>
+      <c r="D19">
+        <v>8.391647231234558</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20">
+        <v>8.391647231234558</v>
+      </c>
+      <c r="C20">
+        <v>9.831636801116716</v>
+      </c>
+      <c r="D20">
+        <v>8.391647231234558</v>
       </c>
     </row>
   </sheetData>
